--- a/lc-balance/analysis/TF_Balance_Component_Mapping-en.xlsx
+++ b/lc-balance/analysis/TF_Balance_Component_Mapping-en.xlsx
@@ -17600,7 +17600,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>FULL amount, no residual. Test T4.</t>
+          <t>FULL amount, no residual. Test T4. Exception: A3S's document-matched partial redeem (businessEventId-linked) is not amount-based — see README Rule #1; standalone (A9) remains full-only.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
